--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>53.6%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.9%</t>
+          <t>-65.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.2%</t>
+          <t>119.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>88.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-532.1%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-59.8%</t>
+          <t>-59.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>86.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>498.6%</t>
+          <t>492.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-392.1%</t>
+          <t>-391.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>32.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.6%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-213.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-32.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>28.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>42.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.2%</t>
+          <t>-160.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>62.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-273.5%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>14.6%</t>
+          <t>37.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.6%</t>
+          <t>-131.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-110.8%</t>
+          <t>-103.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.8%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>93.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-164.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-22.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.1%</t>
+          <t>76.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-70.9%</t>
+          <t>-66.2%</t>
         </is>
       </c>
     </row>
@@ -43733,16 +43733,16 @@
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.858629459151194</v>
+        <v>0.9365721598011831</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.483013301622341</v>
+        <v>3.514190381882336</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.880332741705669</v>
+        <v>1.958275442355658</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.268117587299011</v>
+        <v>4.314883207689005</v>
       </c>
     </row>
     <row r="1835">
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.9360203599593709</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.512227497807956</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.959117205840964</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.313646101642533</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.8303334720170712</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.449778015258483</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.944556132138281</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.28473473004837</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.8361828531323156</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.452606906430455</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.944556132138281</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.285223868774245</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.787960586285232</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.437397982313288</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.896333865291197</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.260370491287661</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.5508290944354369</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.377486470070912</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.896333865291197</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.295311575785203</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.5558666851630234</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.378078946547284</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.951978321557514</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.327275689730332</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.4993970539867266</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.334237475700503</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.895508690381217</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.27214029264829</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.4336296639373146</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.308948128811208</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.895508690381217</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.27315790177876</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.420094180160605</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.29416196728828</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.895508690381217</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.263785933766516</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>0.3383222797328533</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.251535933072418</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.922544263787354</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.270090003765436</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>0.2711131718609756</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.229417606757369</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.922544263787354</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.274855320599139</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>0.2751046246561658</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.228838983994685</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.926535716582544</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.275074988395493</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.1230438062970948</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>3.067506503118444</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.528387285629284</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>4.0341128213286</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.3446657398552123</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.978723946294119</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.490861151941915</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>4.0114633577151</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.5526697982082895</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.900414467506813</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.490861151941915</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>4.016355502269025</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-0.8230697609171749</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.787335938761247</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>1.220461189233029</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.849196980981683</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.162228138505697</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.644756887032288</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.8813028116445072</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.638786253735018</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.490245360233176</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.533888288080064</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.553285589917028</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.462314210437299</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.486908613724205</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.543321737092221</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.5559776223360594</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.472028180297286</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-1.85361966539075</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.397743708469335</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.1892665706695138</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.253107941341091</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.238800056320823</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.242214090910169</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.1892665706695138</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.251650480153955</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.582482829547486</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>2.106510105074121</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>0.0813605186422956</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>3.18867597239224</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-2.940133179785834</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.959556023635039</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.2762898315960525</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.970191820905489</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178245</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-2.946794120007981</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.958664574246439</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.2762898315960525</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.971964747605748</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.378599913157769</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.772275144453929</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.4127073280373195</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.876447137208392</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310982</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-3.705032442025513</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.629986907908922</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.4951755785444677</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.815250961906194</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006534</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-3.706596593135816</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.627941839120766</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.4951755785444677</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.813831553562159</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.070222838036129</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.488978901394882</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.5933972154115935</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.761386131676125</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.06779577350741</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.489204242212201</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.5937299972187451</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.760440977597666</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.476384550688088</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.324530275354689</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.514049255304018</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-4.889367034829182</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.154522714169712</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.509234687775479</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.30575890911618</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.9859600150637906</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.507228738384356</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-5.682435919646024</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.8455479015205318</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.517487429053035</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.37443904309412</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-5.696150783971135</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.8361615209361823</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.51358699419873</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.008975583216115</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.7094365212931915</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.002318774399424</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.511991914253731</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.013788621681452</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.711290281836265</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.003865409102209</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.514842909361268</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.447137729791688</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.5339243340577671</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.003865409102209</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.510816604826864</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-6.830139118534319</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.3806216772391307</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.003865409102209</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.51071450350528</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.205124444705596</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.2331990627420502</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.378850735273487</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.288294823773944</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.564654767209598</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>0.09473723703849934</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.378850735273487</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.293645127071994</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-7.891054795874611</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.0279067544703282</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-1.7052507639385</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>2.105721129830164</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776679</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-7.884578649081051</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.02227454513113569</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.69877461714494</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>2.112648568528068</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407495</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-7.88088772412464</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.02079817514857085</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.69877461714494</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>2.112648568528068</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.085145899454503</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.09698824816187379</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-1.826413561758929</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>2.041578398878317</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.245784925942868</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.1567613042727838</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.019089735411313</v>
+        <v>-1.941147034761325</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.930455249171323</v>
+        <v>1.977220869561316</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.172315094275419</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.1120016701123827</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.945619903743865</v>
+        <v>-1.867677203093876</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.989908849665214</v>
+        <v>2.036674470055206</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.169885439461479</v>
+        <v>-8.09194273881149</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.09647458743929027</v>
+        <v>-0.06529750717929428</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.865247548279935</v>
+        <v>-1.787304847629947</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.052687483691088</v>
+        <v>2.099453104081081</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.358158241827324</v>
+        <v>-8.280215541177334</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.179002873287224</v>
+        <v>-0.1478257930272284</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.865247548279935</v>
+        <v>-1.787304847629947</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.045468318789492</v>
+        <v>2.092233939179485</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.378322883376871</v>
+        <v>-8.300380182726881</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.193740920681019</v>
+        <v>-0.1625638404210235</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.885412189829483</v>
+        <v>-1.807469489179494</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.026697343085787</v>
+        <v>2.07346296347578</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.608147330540696</v>
+        <v>-8.530204629890706</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.2845549097079929</v>
+        <v>-0.2533778294479969</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.048059726899643</v>
+        <v>-1.970117026249655</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.930224610682247</v>
+        <v>1.97699023107224</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.545078098234356</v>
+        <v>-8.467135397584366</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2566334881563423</v>
+        <v>-0.2254564078963464</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.076573289581877</v>
+        <v>-1.998630588931889</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.915810201702022</v>
+        <v>1.962575822092014</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.493062584265543</v>
+        <v>-8.415119883615553</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.231836946882416</v>
+        <v>-0.20065986662242</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.076573289581877</v>
+        <v>-1.998630588931889</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.919800537388422</v>
+        <v>1.966566157778415</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.574354513819747</v>
+        <v>-8.496411813169757</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.2658289456028395</v>
+        <v>-0.2346518653428435</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.076573289581877</v>
+        <v>-1.998630588931889</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.91832531048968</v>
+        <v>1.965090930879674</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.37708510809175</v>
+        <v>-8.29914240744176</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1718677731467682</v>
+        <v>-0.1406906928867726</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.879303883853879</v>
+        <v>-1.801361183203891</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.051740364091352</v>
+        <v>2.098505984481345</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.177933000854651</v>
+        <v>-8.099990300204661</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.1052580638986118</v>
+        <v>-0.07408098363861582</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.713981357904066</v>
+        <v>-1.636038657254077</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.137882746014557</v>
+        <v>2.18464836640455</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.95208784813524</v>
+        <v>-7.87414514748525</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.005340929774638514</v>
+        <v>0.02583615048535703</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.672054682316902</v>
+        <v>-1.594111981666914</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.172617824403064</v>
+        <v>2.219383444793057</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.665813035812546</v>
+        <v>-7.587870335162556</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.1103081397104977</v>
+        <v>0.1414852199704937</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.672054682316902</v>
+        <v>-1.594111981666914</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.173756968959123</v>
+        <v>2.220522589349116</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116215</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.439017208739212</v>
+        <v>-7.361074508089223</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.2036602447019389</v>
+        <v>0.2348373249619349</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.603940737695358</v>
+        <v>-1.525998037045369</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.217259109894157</v>
+        <v>2.26402473028415</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.155108477810463</v>
+        <v>-7.077165777160474</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.322957441312075</v>
+        <v>0.354134521572071</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.603940737695358</v>
+        <v>-1.525998037045369</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.222992814132793</v>
+        <v>2.269758434522786</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.908121227617511</v>
+        <v>-6.830178526967521</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.4120150789953909</v>
+        <v>0.4431921592553865</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.279010786852417</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.361447901854699</v>
+        <v>2.408213522244692</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.644284360413442</v>
+        <v>-6.566341659763452</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.5076663445641105</v>
+        <v>0.5388434248241065</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.279010786852417</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.351564420541792</v>
+        <v>2.398330040931785</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.377042559545045</v>
+        <v>-6.299099858895056</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.6127285044120958</v>
+        <v>0.6439055846720918</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.279010786852417</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.349729860042418</v>
+        <v>2.396495480432411</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.101233396144561</v>
+        <v>-6.023290695494572</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.7227518547988283</v>
+        <v>0.7539289350588243</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.267934179223672</v>
+        <v>-1.189991478573684</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.402841130036197</v>
+        <v>2.44960675042619</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.832165808377582</v>
+        <v>-5.754223107727592</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.831047396051114</v>
+        <v>0.86222447631111</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.9988665914566929</v>
+        <v>-0.9209238908067044</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.564950188841879</v>
+        <v>2.611715809231872</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.568105870054786</v>
+        <v>-5.490163169404796</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.9234110552184802</v>
+        <v>0.9545881354784762</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.7348066531338967</v>
+        <v>-0.6568639524839083</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.710125835673804</v>
+        <v>2.756891456063797</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.861026246549947</v>
+        <v>-4.783083545899958</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.203455870960115</v>
+        <v>1.234632951220111</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.7348066531338967</v>
+        <v>-0.6568639524839083</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.707338802013503</v>
+        <v>2.754104422403496</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.611385216563995</v>
+        <v>-4.533442515914006</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.303655906842337</v>
+        <v>1.334832987102333</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.485165623147945</v>
+        <v>-0.4072229224979566</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.857467043892916</v>
+        <v>2.904232664282909</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.35684331722292</v>
+        <v>-4.27890061657293</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.404839487799524</v>
+        <v>1.43601656805952</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.2306237238068695</v>
+        <v>-0.152681023156881</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.009559004718318</v>
+        <v>3.056324625108311</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.123362094993321</v>
+        <v>-4.045419394343331</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.506156405529216</v>
+        <v>1.537333485789212</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.002857498422729088</v>
+        <v>0.08080019907271752</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.157572166893929</v>
+        <v>3.204337787283922</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.943653564849448</v>
+        <v>-3.865710864199459</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.575147607273806</v>
+        <v>1.606324687533802</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.06002900258542521</v>
+        <v>0.1379717032354136</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.188982859078588</v>
+        <v>3.235748479468581</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860424</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.811378091218562</v>
+        <v>-3.733435390568572</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.623425283473187</v>
+        <v>1.654602363733183</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.1923044762163119</v>
+        <v>0.2702471768663003</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.263715630004147</v>
+        <v>3.31048125039414</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575949</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.620778416545409</v>
+        <v>-3.54283571589542</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.702480214030085</v>
+        <v>1.733657294290081</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.3829041508894647</v>
+        <v>0.4608468515394532</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.380890495495675</v>
+        <v>3.427656115885668</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.371778617861829</v>
+        <v>-3.293835917211839</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.814986474727176</v>
+        <v>1.846163554987172</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.6319039495730454</v>
+        <v>0.7098466502230338</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.543196715929482</v>
+        <v>3.589962336319476</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.180399543000889</v>
+        <v>-3.102456842350899</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.763562175072334</v>
+        <v>1.794739255332329</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.8232830244339855</v>
+        <v>0.9012257250839739</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.530048231246828</v>
+        <v>3.576813851636821</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.770419008457901</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.901372247345262</v>
+        <v>-2.823429546695272</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.923717435211671</v>
+        <v>1.954894515471667</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.8232830244339855</v>
+        <v>0.9012257250839739</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.578592573123914</v>
+        <v>3.625358193513907</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.76033011118081</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.624634072674449</v>
+        <v>-2.54669137202446</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.03779171706599</v>
+        <v>2.068968797325986</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.005099685543911</v>
+        <v>1.0830423861939</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.691061581775864</v>
+        <v>3.737827202165858</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.49774166623938</v>
+        <v>-2.41979896558939</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.07983469338654</v>
+        <v>2.111011773646536</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.131992091978981</v>
+        <v>1.20993479262897</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.758483039383428</v>
+        <v>3.805248659773421</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.418242935835271</v>
+        <v>3.817083957926029</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.305020055474909</v>
+        <v>-2.298123670814005</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.149962725597235</v>
+        <v>2.152721279461597</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.131992091978981</v>
+        <v>1.20993479262897</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.751522427288335</v>
+        <v>3.798288047678328</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>49.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>71.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-19</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.2%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-7.4%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.6%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>492.1%</t>
+          <t>495.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-391.4%</t>
+          <t>-391.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>50.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>28.0%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.1%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-39.6%</t>
+          <t>-41.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-160.9%</t>
+          <t>-163.8%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.6%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-131.4%</t>
+          <t>-144.0%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.2%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-66.2%</t>
+          <t>-69.2%</t>
         </is>
       </c>
     </row>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045693</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43750,7 +43750,7 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831154</v>
+        <v>3.320996253831153</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511404</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386093</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.23380032591164</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.23598197738233</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178245</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310982</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006534</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.37443904309412</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776679</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407495</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880269</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234394</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860583</v>
+        <v>3.493712438860581</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116215</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74769908470241</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906227</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781949</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567244</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487773</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309727</v>
+        <v>3.833249172309725</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858729</v>
+        <v>3.839370871858727</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096474</v>
+        <v>3.856158176096472</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761808</v>
+        <v>3.787326853761806</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.14833294427436</v>
+        <v>3.118374504669057</v>
       </c>
       <c r="D1905" t="n">
         <v>-3.733435390568572</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.654602363733183</v>
+        <v>1.624643924127881</v>
       </c>
       <c r="F1905" t="n">
         <v>0.2702471768663003</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.31048125039414</v>
+        <v>3.280522810788837</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.151148004961996</v>
+        <v>3.121189565356694</v>
       </c>
       <c r="D1906" t="n">
         <v>-3.54283571589542</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.733657294290081</v>
+        <v>1.703698854684779</v>
       </c>
       <c r="F1906" t="n">
         <v>0.4608468515394532</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.427656115885668</v>
+        <v>3.397697676280366</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.164054346185655</v>
+        <v>3.134095906580352</v>
       </c>
       <c r="D1907" t="n">
         <v>-3.293835917211839</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.846163554987172</v>
+        <v>1.816205115381869</v>
       </c>
       <c r="F1907" t="n">
         <v>0.7098466502230338</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.589962336319476</v>
+        <v>3.560003896714173</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.036078416586436</v>
+        <v>3.006119976981133</v>
       </c>
       <c r="D1908" t="n">
         <v>-3.102456842350899</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.794739255332329</v>
+        <v>1.764780815727026</v>
       </c>
       <c r="F1908" t="n">
         <v>0.9012257250839739</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.576813851636821</v>
+        <v>3.546855412031518</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457901</v>
+        <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.084622758463523</v>
+        <v>3.05466431885822</v>
       </c>
       <c r="D1909" t="n">
         <v>-2.823429546695272</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.954894515471667</v>
+        <v>1.924936075866364</v>
       </c>
       <c r="F1909" t="n">
         <v>0.9012257250839739</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.625358193513907</v>
+        <v>3.595399753908604</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.76033011118081</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.088001770449517</v>
+        <v>3.058043330844214</v>
       </c>
       <c r="D1910" t="n">
         <v>-2.54669137202446</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.068968797325986</v>
+        <v>2.039010357720684</v>
       </c>
       <c r="F1910" t="n">
         <v>1.0830423861939</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.737827202165858</v>
+        <v>3.707868762560555</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879203</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.079287784196039</v>
+        <v>3.049329344590736</v>
       </c>
       <c r="D1911" t="n">
         <v>-2.41979896558939</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.111011773646536</v>
+        <v>2.081053334041233</v>
       </c>
       <c r="F1911" t="n">
         <v>1.20993479262897</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.805248659773421</v>
+        <v>3.775290220168118</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.817083957926029</v>
+        <v>3.77893901488367</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.072327172100946</v>
+        <v>3.042368732495643</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.298123670814005</v>
+        <v>-2.295177107027279</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.152721279461597</v>
+        <v>2.123941465370984</v>
       </c>
       <c r="F1912" t="n">
         <v>1.20993479262897</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.798288047678328</v>
+        <v>3.768329608073025</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>25.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>71.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.8%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-8.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-65.5%</t>
+          <t>-66.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>104.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>120.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-532.1%</t>
+          <t>-539.9%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>22.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-42.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-59.4%</t>
+          <t>-61.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>495.8%</t>
+          <t>499.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>0.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-391.1%</t>
+          <t>-408.7%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.3%</t>
+          <t>50.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-213.2%</t>
+          <t>-216.3%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.4%</t>
+          <t>-32.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.9%</t>
+          <t>-38.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-163.8%</t>
+          <t>-171.5%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.6%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-273.5%</t>
+          <t>-281.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-26.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>2.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>-0.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-144.0%</t>
+          <t>-149.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.0%</t>
+          <t>-125.4%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.9%</t>
+          <t>94.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-164.5%</t>
+          <t>-169.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.7%</t>
+          <t>-23.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>1.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-69.2%</t>
+          <t>-83.3%</t>
         </is>
       </c>
     </row>
@@ -43727,22 +43727,22 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045693</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
       </c>
       <c r="D1834" t="n">
-        <v>0.9365721598011831</v>
+        <v>0.858629459151194</v>
       </c>
       <c r="E1834" t="n">
-        <v>3.514190381882336</v>
+        <v>3.483013301622341</v>
       </c>
       <c r="F1834" t="n">
-        <v>1.958275442355658</v>
+        <v>1.880332741705669</v>
       </c>
       <c r="G1834" t="n">
-        <v>4.314883207689005</v>
+        <v>4.268117587299011</v>
       </c>
     </row>
     <row r="1835">
@@ -43750,22 +43750,22 @@
         <v>45297</v>
       </c>
       <c r="B1835" t="n">
-        <v>3.320996253831153</v>
+        <v>3.320996253831154</v>
       </c>
       <c r="C1835" t="n">
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.9360203599593709</v>
+        <v>0.8580776593093818</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.512227497807956</v>
+        <v>3.48105041754796</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.959117205840964</v>
+        <v>1.881174505190975</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.313646101642533</v>
+        <v>4.26688048125254</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.8303334720170712</v>
+        <v>0.7523907713670821</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.449778015258483</v>
+        <v>3.418600934998487</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.944556132138281</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.28473473004837</v>
+        <v>4.237969109658377</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.8361828531323156</v>
+        <v>0.7582401524823265</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.452606906430455</v>
+        <v>3.421429826170459</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.944556132138281</v>
+        <v>1.866613431488292</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.285223868774245</v>
+        <v>4.238458248384251</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511404</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.787960586285232</v>
+        <v>0.7100178856352429</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.437397982313288</v>
+        <v>3.406220902053293</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.896333865291197</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.260370491287661</v>
+        <v>4.213604870897668</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386093</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.5508290944354369</v>
+        <v>0.4728863937854478</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.377486470070912</v>
+        <v>3.346309389810916</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.896333865291197</v>
+        <v>1.818391164641208</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.295311575785203</v>
+        <v>4.24854595539521</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.5558666851630234</v>
+        <v>0.4779239845130344</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.378078946547284</v>
+        <v>3.346901866287289</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.951978321557514</v>
+        <v>1.874035620907526</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.327275689730332</v>
+        <v>4.280510069340338</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4993970539867266</v>
+        <v>0.4214543533367376</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.334237475700503</v>
+        <v>3.303060395440507</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.895508690381217</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.27214029264829</v>
+        <v>4.225374672258297</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.4336296639373146</v>
+        <v>0.3556869632873255</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.308948128811208</v>
+        <v>3.277771048551212</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.895508690381217</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.27315790177876</v>
+        <v>4.226392281388767</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.420094180160605</v>
+        <v>0.3421514795106159</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.29416196728828</v>
+        <v>3.262984887028284</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.895508690381217</v>
+        <v>1.817565989731229</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.263785933766516</v>
+        <v>4.217020313376523</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.29873059070667</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.3383222797328533</v>
+        <v>0.2603795790828642</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.251535933072418</v>
+        <v>3.220358852812422</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.922544263787354</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.270090003765436</v>
+        <v>4.223324383375443</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.2711131718609756</v>
+        <v>0.1931704712109866</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.229417606757369</v>
+        <v>3.198240526497373</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.922544263787354</v>
+        <v>1.844601563137365</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.274855320599139</v>
+        <v>4.228089700209145</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201488</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.2751046246561658</v>
+        <v>0.1971619240061768</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.228838983994685</v>
+        <v>3.19766190373469</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.926535716582544</v>
+        <v>1.848593015932555</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.275074988395493</v>
+        <v>4.228309368005499</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153007</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.1230438062970948</v>
+        <v>-0.2009865069470839</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.067506503118444</v>
+        <v>3.036329422858449</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.528387285629284</v>
+        <v>1.450444584979295</v>
       </c>
       <c r="G1847" t="n">
-        <v>4.0341128213286</v>
+        <v>3.987347200938607</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537426</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.3446657398552123</v>
+        <v>-0.4226084405052014</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.978723946294119</v>
+        <v>2.947546866034124</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.490861151941915</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1848" t="n">
-        <v>4.0114633577151</v>
+        <v>3.964697737325107</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.5526697982082895</v>
+        <v>-0.6306124988582786</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.900414467506813</v>
+        <v>2.869237387246818</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.490861151941915</v>
+        <v>1.412918451291926</v>
       </c>
       <c r="G1849" t="n">
-        <v>4.016355502269025</v>
+        <v>3.969589881879032</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.8230697609171749</v>
+        <v>-0.901012461567164</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.787335938761247</v>
+        <v>2.756158858501252</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.220461189233029</v>
+        <v>1.14251848858304</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.849196980981683</v>
+        <v>3.802431360591689</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.162228138505697</v>
+        <v>-1.240170839155686</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.644756887032288</v>
+        <v>2.613579806772292</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8813028116445072</v>
+        <v>0.8033601109945183</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.638786253735018</v>
+        <v>3.592020633345025</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.490245360233176</v>
+        <v>-1.568188060883165</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.533888288080064</v>
+        <v>2.502711207820068</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.553285589917028</v>
+        <v>0.4753428892670392</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.462314210437299</v>
+        <v>3.415548590047305</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.486908613724205</v>
+        <v>-1.564851314374194</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.543321737092221</v>
+        <v>2.512144656832226</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.5559776223360594</v>
+        <v>0.4780349216860705</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.472028180297286</v>
+        <v>3.425262559907293</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.85361966539075</v>
+        <v>-1.931562366040739</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.397743708469335</v>
+        <v>2.366566628209339</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1892665706695138</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.253107941341091</v>
+        <v>3.206342320951098</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.238800056320823</v>
+        <v>-2.316742756970812</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.242214090910169</v>
+        <v>2.211037010650174</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1892665706695138</v>
+        <v>0.1113238700195249</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.251650480153955</v>
+        <v>3.204884859763961</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.582482829547486</v>
+        <v>-2.660425530197474</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.106510105074121</v>
+        <v>2.075333024814125</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.0813605186422956</v>
+        <v>0.003417817992306726</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.18867597239224</v>
+        <v>3.141910352002246</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130019</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-2.940133179785834</v>
+        <v>-3.018075880435823</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.959556023635039</v>
+        <v>1.928378943375043</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.2762898315960525</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.970191820905489</v>
+        <v>2.923426200515495</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-2.946794120007981</v>
+        <v>-3.02473682065797</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.958664574246439</v>
+        <v>1.927487493986444</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.2762898315960525</v>
+        <v>-0.3542325322460414</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.971964747605748</v>
+        <v>2.925199127215755</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.378599913157769</v>
+        <v>-3.456542613807758</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.772275144453929</v>
+        <v>1.741098064193933</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4127073280373195</v>
+        <v>-0.4906500286873084</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.876447137208392</v>
+        <v>2.829681516818399</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.705032442025513</v>
+        <v>-3.782975142675502</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.629986907908922</v>
+        <v>1.598809827648927</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.4951755785444677</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.815250961906194</v>
+        <v>2.768485341516201</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.706596593135816</v>
+        <v>-3.784539293785805</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.627941839120766</v>
+        <v>1.596764758860771</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.4951755785444677</v>
+        <v>-0.5731182791944566</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.813831553562159</v>
+        <v>2.767065933172166</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.070222838036129</v>
+        <v>-4.148165538686118</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.488978901394882</v>
+        <v>1.457801821134887</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.5933972154115935</v>
+        <v>-0.6713399160615824</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.761386131676125</v>
+        <v>2.714620511286132</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.06779577350741</v>
+        <v>-4.145738474157399</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.489204242212201</v>
+        <v>1.458027161952206</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.5937299972187451</v>
+        <v>-0.671672697868734</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.760440977597666</v>
+        <v>2.713675357207673</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.476384550688088</v>
+        <v>-4.554327251338078</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.324530275354689</v>
+        <v>1.293353195094693</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.514049255304018</v>
+        <v>2.467283634914025</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.889367034829182</v>
+        <v>-4.967309735479172</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.154522714169712</v>
+        <v>1.123345633909716</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.509234687775479</v>
+        <v>2.462469067385485</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.30575890911618</v>
+        <v>-5.383701609766169</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9859600150637906</v>
+        <v>0.9547829348037946</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.507228738384356</v>
+        <v>2.460463117994363</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.682435919646024</v>
+        <v>-5.760378620296014</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8455479015205318</v>
+        <v>0.8143708212605358</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.517487429053035</v>
+        <v>2.470721808663042</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.696150783971135</v>
+        <v>-5.774093484621125</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8361615209361823</v>
+        <v>0.8049844406761864</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.51358699419873</v>
+        <v>2.466821373808737</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.008975583216115</v>
+        <v>-6.086918283866105</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.7094365212931915</v>
+        <v>0.6782594410331955</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.002318774399424</v>
+        <v>-1.080261475049412</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.511991914253731</v>
+        <v>2.465226293863738</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.013788621681452</v>
+        <v>-6.091731322331442</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.711290281836265</v>
+        <v>0.680113201576269</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.003865409102209</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.514842909361268</v>
+        <v>2.468077288971275</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.447137729791688</v>
+        <v>-6.525080430441678</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5339243340577671</v>
+        <v>0.5027472537977715</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.003865409102209</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.510816604826864</v>
+        <v>2.464050984436871</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.830139118534319</v>
+        <v>-6.908081819184309</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3806216772391307</v>
+        <v>0.3494445969791347</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.003865409102209</v>
+        <v>-1.081808109752198</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.51071450350528</v>
+        <v>2.463948883115287</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.205124444705596</v>
+        <v>-7.283067145355586</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2331990627420502</v>
+        <v>0.2020219824820542</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.378850735273487</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.288294823773944</v>
+        <v>2.241529203383951</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.564654767209598</v>
+        <v>-7.642597467859588</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.09473723703849934</v>
+        <v>0.0635601567785038</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.378850735273487</v>
+        <v>-1.456793435923476</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.293645127071994</v>
+        <v>2.246879506682001</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.891054795874611</v>
+        <v>-7.968997496524601</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.0279067544703282</v>
+        <v>-0.05908383473032419</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.7052507639385</v>
+        <v>-1.783193464588488</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.105721129830164</v>
+        <v>2.058955509440171</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.884578649081051</v>
+        <v>-7.962521349731041</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.02227454513113569</v>
+        <v>-0.05345162539113124</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.69877461714494</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.112648568528068</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.88088772412464</v>
+        <v>-7.95883042477463</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.02079817514857085</v>
+        <v>-0.05197525540856685</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.69877461714494</v>
+        <v>-1.776717317794929</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.112648568528068</v>
+        <v>2.065882948138076</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.085145899454503</v>
+        <v>-8.163088600104492</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.09698824816187379</v>
+        <v>-0.1281653284218693</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.826413561758929</v>
+        <v>-1.904356262408918</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.041578398878317</v>
+        <v>1.994812778488325</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.245784925942868</v>
+        <v>-8.323727626592857</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1567613042727838</v>
+        <v>-0.1879383845327793</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.941147034761325</v>
+        <v>-2.019089735411313</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.977220869561316</v>
+        <v>1.930455249171323</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.172315094275419</v>
+        <v>-8.250257794925409</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1120016701123827</v>
+        <v>-0.1431787503723787</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.867677203093876</v>
+        <v>-1.945619903743865</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.036674470055206</v>
+        <v>1.989908849665214</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.09194273881149</v>
+        <v>-8.169885439461479</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.06529750717929428</v>
+        <v>-0.09647458743929027</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.787304847629947</v>
+        <v>-1.865247548279935</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.099453104081081</v>
+        <v>2.052687483691088</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.280215541177334</v>
+        <v>-8.358158241827324</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.1478257930272284</v>
+        <v>-0.179002873287224</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.787304847629947</v>
+        <v>-1.865247548279935</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.092233939179485</v>
+        <v>2.045468318789492</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.300380182726881</v>
+        <v>-8.378322883376871</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.1625638404210235</v>
+        <v>-0.193740920681019</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.807469489179494</v>
+        <v>-1.885412189829483</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.07346296347578</v>
+        <v>2.026697343085787</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860581</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.530204629890706</v>
+        <v>-8.608147330540696</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.2533778294479969</v>
+        <v>-0.2845549097079929</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.970117026249655</v>
+        <v>-2.048059726899643</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.97699023107224</v>
+        <v>1.930224610682247</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.467135397584366</v>
+        <v>-8.545078098234356</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2254564078963464</v>
+        <v>-0.2566334881563423</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.998630588931889</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.962575822092014</v>
+        <v>1.915810201702022</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.415119883615553</v>
+        <v>-8.493062584265543</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.20065986662242</v>
+        <v>-0.231836946882416</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.998630588931889</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.966566157778415</v>
+        <v>1.919800537388422</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.496411813169757</v>
+        <v>-8.574354513819747</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.2346518653428435</v>
+        <v>-0.2658289456028395</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.998630588931889</v>
+        <v>-2.076573289581877</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.965090930879674</v>
+        <v>1.91832531048968</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.29914240744176</v>
+        <v>-8.37708510809175</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1406906928867726</v>
+        <v>-0.1718677731467682</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.801361183203891</v>
+        <v>-1.879303883853879</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.098505984481345</v>
+        <v>2.051740364091352</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.099990300204661</v>
+        <v>-8.177933000854651</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.07408098363861582</v>
+        <v>-0.1052580638986118</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.636038657254077</v>
+        <v>-1.713981357904066</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.18464836640455</v>
+        <v>2.137882746014557</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.87414514748525</v>
+        <v>-7.95208784813524</v>
       </c>
       <c r="E1890" t="n">
-        <v>0.02583615048535703</v>
+        <v>-0.005340929774638514</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.594111981666914</v>
+        <v>-1.672054682316902</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.219383444793057</v>
+        <v>2.172617824403064</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.587870335162556</v>
+        <v>-7.665813035812546</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.1414852199704937</v>
+        <v>0.1103081397104977</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.594111981666914</v>
+        <v>-1.672054682316902</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.220522589349116</v>
+        <v>2.173756968959123</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.361074508089223</v>
+        <v>-7.439017208739212</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.2348373249619349</v>
+        <v>0.2036602447019389</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.525998037045369</v>
+        <v>-1.603940737695358</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.26402473028415</v>
+        <v>2.217259109894157</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.077165777160474</v>
+        <v>-7.155108477810463</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.354134521572071</v>
+        <v>0.322957441312075</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.525998037045369</v>
+        <v>-1.603940737695358</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.269758434522786</v>
+        <v>2.222992814132793</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.830178526967521</v>
+        <v>-6.908121227617511</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.4431921592553865</v>
+        <v>0.4120150789953909</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.279010786852417</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.408213522244692</v>
+        <v>2.361447901854699</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.566341659763452</v>
+        <v>-6.644284360413442</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.5388434248241065</v>
+        <v>0.5076663445641105</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.279010786852417</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.398330040931785</v>
+        <v>2.351564420541792</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.299099858895056</v>
+        <v>-6.377042559545045</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.6439055846720918</v>
+        <v>0.6127285044120958</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.279010786852417</v>
+        <v>-1.356953487502406</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.396495480432411</v>
+        <v>2.349729860042418</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.023290695494572</v>
+        <v>-6.101233396144561</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.7539289350588243</v>
+        <v>0.7227518547988283</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.189991478573684</v>
+        <v>-1.267934179223672</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.44960675042619</v>
+        <v>2.402841130036197</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.754223107727592</v>
+        <v>-5.832165808377582</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.86222447631111</v>
+        <v>0.831047396051114</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.9209238908067044</v>
+        <v>-0.9988665914566929</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.611715809231872</v>
+        <v>2.564950188841879</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.490163169404796</v>
+        <v>-5.568105870054786</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.9545881354784762</v>
+        <v>0.9234110552184802</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.6568639524839083</v>
+        <v>-0.7348066531338967</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.756891456063797</v>
+        <v>2.710125835673804</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.783083545899958</v>
+        <v>-4.861026246549947</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.234632951220111</v>
+        <v>1.203455870960115</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.6568639524839083</v>
+        <v>-0.7348066531338967</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.754104422403496</v>
+        <v>2.707338802013503</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.533442515914006</v>
+        <v>-4.611385216563995</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.334832987102333</v>
+        <v>1.303655906842337</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.4072229224979566</v>
+        <v>-0.485165623147945</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.904232664282909</v>
+        <v>2.857467043892916</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.27890061657293</v>
+        <v>-4.35684331722292</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.43601656805952</v>
+        <v>1.404839487799524</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.152681023156881</v>
+        <v>-0.2306237238068695</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.056324625108311</v>
+        <v>3.009559004718318</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.045419394343331</v>
+        <v>-4.123362094993321</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.537333485789212</v>
+        <v>1.506156405529216</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.08080019907271752</v>
+        <v>0.002857498422729088</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.204337787283922</v>
+        <v>3.157572166893929</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.865710864199459</v>
+        <v>-3.943653564849448</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.606324687533802</v>
+        <v>1.575147607273806</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.1379717032354136</v>
+        <v>0.06002900258542521</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.235748479468581</v>
+        <v>3.188982859078588</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.118374504669057</v>
+        <v>3.112094084840844</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.733435390568572</v>
+        <v>-3.957825343699237</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.624643924127881</v>
+        <v>1.528607523047401</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.2702471768663003</v>
+        <v>0.0458572237356365</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.280522810788837</v>
+        <v>3.139608419082226</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.121189565356694</v>
+        <v>3.11490914552848</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.54283571589542</v>
+        <v>-3.767225669026084</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.703698854684779</v>
+        <v>1.607662453604299</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.4608468515394532</v>
+        <v>0.2364568984087894</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.397697676280366</v>
+        <v>3.256783284573754</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.134095906580352</v>
+        <v>3.127815486752139</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.293835917211839</v>
+        <v>-3.518225870342504</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.816205115381869</v>
+        <v>1.72016871430139</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.7098466502230338</v>
+        <v>0.48545669709237</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.560003896714173</v>
+        <v>3.419089505007561</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.006119976981133</v>
+        <v>2.99983955715292</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.102456842350899</v>
+        <v>-3.326846795481563</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.764780815727026</v>
+        <v>1.668744414646547</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.9012257250839739</v>
+        <v>0.6768357719533101</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.546855412031518</v>
+        <v>3.405941020324906</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.05466431885822</v>
+        <v>3.048383899030006</v>
       </c>
       <c r="D1909" t="n">
-        <v>-2.823429546695272</v>
+        <v>-3.047819499825937</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.924936075866364</v>
+        <v>1.828899674785884</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.9012257250839739</v>
+        <v>0.6768357719533101</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.595399753908604</v>
+        <v>3.454485362201992</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.058043330844214</v>
+        <v>3.051762911016001</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.54669137202446</v>
+        <v>-2.771081325155124</v>
       </c>
       <c r="E1910" t="n">
-        <v>2.039010357720684</v>
+        <v>1.942973956640204</v>
       </c>
       <c r="F1910" t="n">
-        <v>1.0830423861939</v>
+        <v>0.8586524330632359</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.707868762560555</v>
+        <v>3.566954370853943</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.049329344590736</v>
+        <v>3.043048924762523</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.41979896558939</v>
+        <v>-2.644188918720054</v>
       </c>
       <c r="E1911" t="n">
-        <v>2.081053334041233</v>
+        <v>1.985016932960754</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.20993479262897</v>
+        <v>0.9855448394983058</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.775290220168118</v>
+        <v>3.634375828461506</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.77893901488367</v>
+        <v>3.538194474635699</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.042368732495643</v>
+        <v>3.03608831266743</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.295177107027279</v>
+        <v>-2.471629025020859</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.123941465370984</v>
+        <v>2.047080278345339</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.20993479262897</v>
+        <v>0.9855448394983058</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.768329608073025</v>
+        <v>3.627415216366413</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>71.2%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>17.8%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,15 +811,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-19</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-29.2%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-68.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>104.8%</t>
+          <t>105.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.2%</t>
+          <t>120.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.5%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.9%</t>
+          <t>23.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-42.2%</t>
+          <t>-43.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-61.0%</t>
+          <t>-63.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>87.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>499.8%</t>
+          <t>497.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-408.7%</t>
+          <t>-432.1%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.7%</t>
+          <t>98.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-32.7%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>26.1%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-38.0%</t>
+          <t>-48.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-171.5%</t>
+          <t>-177.2%</t>
         </is>
       </c>
     </row>
@@ -1232,26 +1232,26 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-10.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.0%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.5%</t>
+          <t>99.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-26.8%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.5%</t>
+          <t>687.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-149.6%</t>
+          <t>-148.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-125.4%</t>
+          <t>-150.3%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-23</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>74.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.2%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.1%</t>
+          <t>-24.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.3%</t>
+          <t>-13.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-83.3%</t>
+          <t>-164.3%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1912"/>
+  <dimension ref="A1:G1913"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279815</v>
+        <v>3.385382209279814</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511406</v>
+        <v>3.367379938511405</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386095</v>
+        <v>3.376932391386094</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.36737053999856</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082126</v>
+        <v>3.299560092082125</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43957,7 +43957,7 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.29873059070667</v>
+        <v>3.298730590706669</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
@@ -43980,7 +43980,7 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296838</v>
+        <v>3.299918119296837</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201488</v>
+        <v>3.295507330201487</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153007</v>
+        <v>3.258791981153006</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537426</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382191</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416046</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347057</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130019</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969596</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923089</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.458100091297751</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.250257794925409</v>
+        <v>-8.5067562600158</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.1431787503723787</v>
+        <v>-0.2457781364085356</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.945619903743865</v>
+        <v>-2.202118368834256</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.989908849665214</v>
+        <v>1.836009770610978</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.169885439461479</v>
+        <v>-8.426383904551871</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.09647458743929027</v>
+        <v>-0.1990739734754472</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.865247548279935</v>
+        <v>-2.121746013370327</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.052687483691088</v>
+        <v>1.898788404636853</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.358158241827324</v>
+        <v>-8.614656706917716</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.179002873287224</v>
+        <v>-0.2816022593233809</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.865247548279935</v>
+        <v>-2.121746013370327</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.045468318789492</v>
+        <v>1.891569239735257</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.378322883376871</v>
+        <v>-8.634821348467263</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.193740920681019</v>
+        <v>-0.2963403067171759</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.885412189829483</v>
+        <v>-2.141910654919875</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.026697343085787</v>
+        <v>1.872798264031552</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.608147330540696</v>
+        <v>-8.864645795631088</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.2845549097079929</v>
+        <v>-0.3871542957441494</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.048059726899643</v>
+        <v>-2.304558191990035</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.930224610682247</v>
+        <v>1.776325531628012</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.545078098234356</v>
+        <v>-8.801576563324748</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.2566334881563423</v>
+        <v>-0.3592328741924988</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.076573289581877</v>
+        <v>-2.333071754672269</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.915810201702022</v>
+        <v>1.761911122647786</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.493062584265543</v>
+        <v>-8.749561049355934</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.231836946882416</v>
+        <v>-0.3344363329185729</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.076573289581877</v>
+        <v>-2.333071754672269</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.919800537388422</v>
+        <v>1.765901458334187</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628916</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.574354513819747</v>
+        <v>-8.830852978910139</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.2658289456028395</v>
+        <v>-0.368428331638996</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.076573289581877</v>
+        <v>-2.333071754672269</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.91832531048968</v>
+        <v>1.764426231435445</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410713</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.37708510809175</v>
+        <v>-8.633583573182142</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.1718677731467682</v>
+        <v>-0.2744671591829251</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.879303883853879</v>
+        <v>-2.135802348944271</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.051740364091352</v>
+        <v>1.897841285037116</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240573</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.177933000854651</v>
+        <v>-8.434431465945043</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.1052580638986118</v>
+        <v>-0.2078574499347683</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.713981357904066</v>
+        <v>-1.970479822994458</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.137882746014557</v>
+        <v>1.983983666960321</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085276</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-7.95208784813524</v>
+        <v>-8.208586313225631</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.005340929774638514</v>
+        <v>-0.107940315810795</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.672054682316902</v>
+        <v>-1.928553147407294</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.172617824403064</v>
+        <v>2.018718745348829</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.665813035812546</v>
+        <v>-7.922311500902937</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.1103081397104977</v>
+        <v>0.007708753674341651</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.672054682316902</v>
+        <v>-1.928553147407294</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.173756968959123</v>
+        <v>2.019857889904888</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.439017208739212</v>
+        <v>-7.695515673829602</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.2036602447019389</v>
+        <v>0.1010608586657828</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.603940737695358</v>
+        <v>-1.86043920278575</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.217259109894157</v>
+        <v>2.063360030839922</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081565</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.155108477810463</v>
+        <v>-7.411606942900853</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.322957441312075</v>
+        <v>0.220358055275919</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.603940737695358</v>
+        <v>-1.86043920278575</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.222992814132793</v>
+        <v>2.069093735078558</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-6.908121227617511</v>
+        <v>-7.164619692707901</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.4120150789953909</v>
+        <v>0.3094156929592349</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.613451952592798</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.361447901854699</v>
+        <v>2.207548822800464</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.644284360413442</v>
+        <v>-6.900782825503832</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.5076663445641105</v>
+        <v>0.4050669585279549</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.613451952592798</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.351564420541792</v>
+        <v>2.197665341487556</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.377042559545045</v>
+        <v>-6.633541024635435</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.6127285044120958</v>
+        <v>0.5101291183759398</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.356953487502406</v>
+        <v>-1.613451952592798</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.349729860042418</v>
+        <v>2.195830780988183</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.101233396144561</v>
+        <v>-6.357731861234951</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.7227518547988283</v>
+        <v>0.6201524687626727</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.267934179223672</v>
+        <v>-1.524432644314064</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.402841130036197</v>
+        <v>2.248942050981962</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-5.832165808377582</v>
+        <v>-6.088664273467971</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.831047396051114</v>
+        <v>0.728448010014958</v>
       </c>
       <c r="F1898" t="n">
-        <v>-0.9988665914566929</v>
+        <v>-1.255365056547085</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.564950188841879</v>
+        <v>2.411051109787643</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.568105870054786</v>
+        <v>-5.824604335145176</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.9234110552184802</v>
+        <v>0.8208116691823242</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.7348066531338967</v>
+        <v>-0.9913051182242889</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.710125835673804</v>
+        <v>2.556226756619569</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-4.861026246549947</v>
+        <v>-5.117524711640337</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.203455870960115</v>
+        <v>1.100856484923959</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.7348066531338967</v>
+        <v>-0.9913051182242889</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.707338802013503</v>
+        <v>2.553439722959268</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.611385216563995</v>
+        <v>-4.867883681654385</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.303655906842337</v>
+        <v>1.201056520806181</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.485165623147945</v>
+        <v>-0.7416640882383372</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.857467043892916</v>
+        <v>2.70356796483868</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.35684331722292</v>
+        <v>-4.613341782313309</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.404839487799524</v>
+        <v>1.302240101763368</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.2306237238068695</v>
+        <v>-0.4871221888972617</v>
       </c>
       <c r="G1902" t="n">
-        <v>3.009559004718318</v>
+        <v>2.855659925664082</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.123362094993321</v>
+        <v>-4.379860560083711</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.506156405529216</v>
+        <v>1.40355701949306</v>
       </c>
       <c r="F1903" t="n">
-        <v>0.002857498422729088</v>
+        <v>-0.2536409666676631</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.157572166893929</v>
+        <v>3.003673087839694</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-3.943653564849448</v>
+        <v>-4.200152029939838</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.575147607273806</v>
+        <v>1.47254822123765</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.06002900258542521</v>
+        <v>-0.196469462504967</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.188982859078588</v>
+        <v>3.035083780024352</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763178672860423</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.112094084840844</v>
+        <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-3.957825343699237</v>
+        <v>-4.206402794308332</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.528607523047401</v>
+        <v>1.46541540223728</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.0458572237356365</v>
+        <v>-0.2027202268734603</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.139608419082226</v>
+        <v>3.026700808150284</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784715218575948</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.11490914552848</v>
+        <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.767225669026084</v>
+        <v>-4.015803119635179</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.607662453604299</v>
+        <v>1.544470332794177</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.2364568984087894</v>
+        <v>-0.01212055220030744</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.256783284573754</v>
+        <v>3.143875673641812</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753878996430982</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.127815486752139</v>
+        <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.518225870342504</v>
+        <v>-3.766803320951599</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.72016871430139</v>
+        <v>1.656976593491268</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.48545669709237</v>
+        <v>0.2368792464832732</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.419089505007561</v>
+        <v>3.306181894075619</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.69292828007764</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.99983955715292</v>
+        <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.326846795481563</v>
+        <v>-3.575424246090658</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.668744414646547</v>
+        <v>1.605552293836426</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.6768357719533101</v>
+        <v>0.4282583213442133</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.405941020324906</v>
+        <v>3.293033409392964</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770419008457898</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.048383899030006</v>
+        <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.047819499825937</v>
+        <v>-3.296396950435032</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.828899674785884</v>
+        <v>1.765707553975763</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.6768357719533101</v>
+        <v>0.4282583213442133</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.454485362201992</v>
+        <v>3.341577751270051</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
-        <v>3.051762911016001</v>
+        <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.771081325155124</v>
+        <v>-3.019658775764219</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.942973956640204</v>
+        <v>1.879781835830082</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.8586524330632359</v>
+        <v>0.6100749824541392</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.566954370853943</v>
+        <v>3.454046759922001</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
-        <v>3.043048924762523</v>
+        <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.644188918720054</v>
+        <v>-2.892766369329149</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.985016932960754</v>
+        <v>1.921824812150632</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.9855448394983058</v>
+        <v>0.7369673888892091</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.634375828461506</v>
+        <v>3.521468217529565</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,45 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.538194474635699</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
-        <v>3.03608831266743</v>
+        <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.471629025020859</v>
+        <v>-2.705178861419223</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.047080278345339</v>
+        <v>1.98989920321951</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.9855448394983058</v>
+        <v>0.7369673888892091</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.627415216366413</v>
+        <v>3.514507605434471</v>
+      </c>
+    </row>
+    <row r="1913">
+      <c r="A1913" s="2" t="n">
+        <v>45375</v>
+      </c>
+      <c r="B1913" t="n">
+        <v>3.420132858879228</v>
+      </c>
+      <c r="C1913" t="n">
+        <v>2.824482646428221</v>
+      </c>
+      <c r="D1913" t="n">
+        <v>-2.705178861419223</v>
+      </c>
+      <c r="E1913" t="n">
+        <v>1.98989920321951</v>
+      </c>
+      <c r="F1913" t="n">
+        <v>0.7369673888892091</v>
+      </c>
+      <c r="G1913" t="n">
+        <v>2.817546443414589</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>13.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-34.2%</t>
+          <t>-35.0%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-29.2%</t>
+          <t>-30.0%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-67.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.0%</t>
+          <t>105.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>120.6%</t>
+          <t>121.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>88.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-539.9%</t>
+          <t>-567.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.0%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.1%</t>
+          <t>-43.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-63.5%</t>
+          <t>-62.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.1%</t>
+          <t>87.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>497.5%</t>
+          <t>653.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-432.1%</t>
+          <t>-419.8%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-227.2%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.7%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>25.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-48.1%</t>
+          <t>-35.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-177.2%</t>
+          <t>-172.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-10.8%</t>
+          <t>-4.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>71.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.6%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-285.6%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>687.6%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-148.8%</t>
+          <t>-151.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-150.3%</t>
+          <t>-115.1%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>74.2%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>97.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-24</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-169.2%</t>
+          <t>-171.8%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.4%</t>
+          <t>-13.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.3%</t>
+          <t>-165.0%</t>
         </is>
       </c>
     </row>
@@ -43756,16 +43756,16 @@
         <v>3.138175778137954</v>
       </c>
       <c r="D1835" t="n">
-        <v>0.8580776593093818</v>
+        <v>0.5864252759317675</v>
       </c>
       <c r="E1835" t="n">
-        <v>3.48105041754796</v>
+        <v>3.372389464196914</v>
       </c>
       <c r="F1835" t="n">
-        <v>1.881174505190975</v>
+        <v>1.83791595995543</v>
       </c>
       <c r="G1835" t="n">
-        <v>4.26688048125254</v>
+        <v>4.240925354111212</v>
       </c>
     </row>
     <row r="1836">
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.7523907713670821</v>
+        <v>0.4807383879894678</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.418600934998487</v>
+        <v>3.309939981647442</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.866613431488292</v>
+        <v>1.823354886252747</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.237969109658377</v>
+        <v>4.21201398251705</v>
       </c>
     </row>
     <row r="1837">
@@ -43796,22 +43796,22 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279814</v>
+        <v>3.385382209279815</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.7582401524823265</v>
+        <v>0.4865877691047122</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.421429826170459</v>
+        <v>3.312768872819414</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.866613431488292</v>
+        <v>1.823354886252747</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.238458248384251</v>
+        <v>4.212503121242924</v>
       </c>
     </row>
     <row r="1838">
@@ -43819,22 +43819,22 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511405</v>
+        <v>3.367379938511406</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.7100178856352429</v>
+        <v>0.4383655022576287</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.406220902053293</v>
+        <v>3.297559948702247</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.818391164641208</v>
+        <v>1.775132619405663</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.213604870897668</v>
+        <v>4.18764974375634</v>
       </c>
     </row>
     <row r="1839">
@@ -43842,22 +43842,22 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386094</v>
+        <v>3.376932391386095</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.4728863937854478</v>
+        <v>0.2012340104078336</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.346309389810916</v>
+        <v>3.237648436459871</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.818391164641208</v>
+        <v>1.775132619405663</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.24854595539521</v>
+        <v>4.222590828253883</v>
       </c>
     </row>
     <row r="1840">
@@ -43865,22 +43865,22 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.36737053999856</v>
+        <v>3.367370539998561</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.4779239845130344</v>
+        <v>0.2062716011354201</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.346901866287289</v>
+        <v>3.238240912936243</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.874035620907526</v>
+        <v>1.83077707567198</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.280510069340338</v>
+        <v>4.254554942199011</v>
       </c>
     </row>
     <row r="1841">
@@ -43888,22 +43888,22 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082125</v>
+        <v>3.299560092082126</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.4214543533367376</v>
+        <v>0.1498019699591233</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.303060395440507</v>
+        <v>3.194399442089462</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.817565989731229</v>
+        <v>1.774307444495683</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.225374672258297</v>
+        <v>4.19941954511697</v>
       </c>
     </row>
     <row r="1842">
@@ -43911,22 +43911,22 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757923</v>
+        <v>3.293490533757924</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.3556869632873255</v>
+        <v>0.08403457990971125</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.277771048551212</v>
+        <v>3.169110095200167</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.817565989731229</v>
+        <v>1.774307444495683</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.226392281388767</v>
+        <v>4.20043715424744</v>
       </c>
     </row>
     <row r="1843">
@@ -43934,22 +43934,22 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760741</v>
+        <v>3.293766719760742</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.3421514795106159</v>
+        <v>0.07049909613300165</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.262984887028284</v>
+        <v>3.154323933677239</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.817565989731229</v>
+        <v>1.774307444495683</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.217020313376523</v>
+        <v>4.191065186235195</v>
       </c>
     </row>
     <row r="1844">
@@ -43957,22 +43957,22 @@
         <v>45306</v>
       </c>
       <c r="B1844" t="n">
-        <v>3.298730590706669</v>
+        <v>3.298730590706671</v>
       </c>
       <c r="C1844" t="n">
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>0.2603795790828642</v>
+        <v>-0.01127280429475003</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.220358852812422</v>
+        <v>3.111697899461376</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.844601563137365</v>
+        <v>1.80134301790182</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.223324383375443</v>
+        <v>4.197369256234116</v>
       </c>
     </row>
     <row r="1845">
@@ -43980,22 +43980,22 @@
         <v>45307</v>
       </c>
       <c r="B1845" t="n">
-        <v>3.299918119296837</v>
+        <v>3.299918119296838</v>
       </c>
       <c r="C1845" t="n">
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>0.1931704712109866</v>
+        <v>-0.0784819121666277</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.198240526497373</v>
+        <v>3.089579573146327</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.844601563137365</v>
+        <v>1.80134301790182</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.228089700209145</v>
+        <v>4.202134573067818</v>
       </c>
     </row>
     <row r="1846">
@@ -44003,22 +44003,22 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201487</v>
+        <v>3.295507330201489</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>0.1971619240061768</v>
+        <v>-0.0744904593714375</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.19766190373469</v>
+        <v>3.089000950383644</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.848593015932555</v>
+        <v>1.80533447069701</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.228309368005499</v>
+        <v>4.202354240864173</v>
       </c>
     </row>
     <row r="1847">
@@ -44026,22 +44026,22 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153006</v>
+        <v>3.258791981153008</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.2009865069470839</v>
+        <v>-0.4726388903246981</v>
       </c>
       <c r="E1847" t="n">
-        <v>3.036329422858449</v>
+        <v>2.927668469507403</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.450444584979295</v>
+        <v>1.407186039743749</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.987347200938607</v>
+        <v>3.961392073797279</v>
       </c>
     </row>
     <row r="1848">
@@ -44049,22 +44049,22 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537427</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.4226084405052014</v>
+        <v>-0.6942608238828156</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.947546866034124</v>
+        <v>2.838885912683078</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.412918451291926</v>
+        <v>1.36965990605638</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.964697737325107</v>
+        <v>3.938742610183779</v>
       </c>
     </row>
     <row r="1849">
@@ -44072,22 +44072,22 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382191</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.6306124988582786</v>
+        <v>-0.9022648822358929</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.869237387246818</v>
+        <v>2.760576433895772</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.412918451291926</v>
+        <v>1.36965990605638</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.969589881879032</v>
+        <v>3.943634754737705</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-0.901012461567164</v>
+        <v>-1.172664844944778</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.756158858501252</v>
+        <v>2.647497905150206</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.14251848858304</v>
+        <v>1.099259943347495</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.802431360591689</v>
+        <v>3.776476233450362</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.240170839155686</v>
+        <v>-1.5118232225333</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.613579806772292</v>
+        <v>2.504918853421246</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.8033601109945183</v>
+        <v>0.7601015657589729</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.592020633345025</v>
+        <v>3.566065506203698</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.568188060883165</v>
+        <v>-1.839840444260779</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.502711207820068</v>
+        <v>2.394050254469023</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4753428892670392</v>
+        <v>0.4320843440314938</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.415548590047305</v>
+        <v>3.389593462905979</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.564851314374194</v>
+        <v>-1.836503697751808</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.512144656832226</v>
+        <v>2.40348370348118</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4780349216860705</v>
+        <v>0.4347763764505251</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.425262559907293</v>
+        <v>3.399307432765966</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-1.931562366040739</v>
+        <v>-2.203214749418353</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.366566628209339</v>
+        <v>2.257905674858294</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.06806532478397953</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.206342320951098</v>
+        <v>3.180387193809771</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.316742756970812</v>
+        <v>-2.588395140348426</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.211037010650174</v>
+        <v>2.102376057299129</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.1113238700195249</v>
+        <v>0.06806532478397953</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.204884859763961</v>
+        <v>3.178929732622634</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.660425530197474</v>
+        <v>-2.932077913575089</v>
       </c>
       <c r="E1856" t="n">
-        <v>2.075333024814125</v>
+        <v>1.966672071463079</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.003417817992306726</v>
+        <v>-0.03984072724323867</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.141910352002246</v>
+        <v>3.115955224860919</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.018075880435823</v>
+        <v>-3.289728263813437</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.928378943375043</v>
+        <v>1.819717990023998</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.3974910774815868</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.923426200515495</v>
+        <v>2.897471073374168</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.02473682065797</v>
+        <v>-3.296389204035584</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.927487493986444</v>
+        <v>1.818826540635398</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3542325322460414</v>
+        <v>-0.3974910774815868</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.925199127215755</v>
+        <v>2.899244000074428</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.456542613807758</v>
+        <v>-3.728194997185372</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.741098064193933</v>
+        <v>1.632437110842887</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.4906500286873084</v>
+        <v>-0.5339085739228537</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.829681516818399</v>
+        <v>2.803726389677072</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-3.782975142675502</v>
+        <v>-4.054627526053116</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.598809827648927</v>
+        <v>1.490148874297881</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.6163768244300019</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.768485341516201</v>
+        <v>2.742530214374874</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-3.784539293785805</v>
+        <v>-4.056191677163419</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.596764758860771</v>
+        <v>1.488103805509724</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.5731182791944566</v>
+        <v>-0.6163768244300019</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.767065933172166</v>
+        <v>2.741110806030839</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.148165538686118</v>
+        <v>-4.419817922063732</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.457801821134887</v>
+        <v>1.349140867783841</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.6713399160615824</v>
+        <v>-0.7145984612971277</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.714620511286132</v>
+        <v>2.688665384144805</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.145738474157399</v>
+        <v>-4.417390857535014</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.458027161952206</v>
+        <v>1.34936620860116</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.671672697868734</v>
+        <v>-0.7149312431042794</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.713675357207673</v>
+        <v>2.687720230066345</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.554327251338078</v>
+        <v>-4.825979634715693</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.293353195094693</v>
+        <v>1.184692241743647</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.467283634914025</v>
+        <v>2.441328507772697</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-4.967309735479172</v>
+        <v>-5.238962118856787</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.123345633909716</v>
+        <v>1.01468468055867</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.462469067385485</v>
+        <v>2.436513940244158</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.383701609766169</v>
+        <v>-5.655353993143784</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.9547829348037946</v>
+        <v>0.8461219814527485</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.460463117994363</v>
+        <v>2.434507990853035</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-5.760378620296014</v>
+        <v>-6.032031003673628</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.8143708212605358</v>
+        <v>0.7057098679094898</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.470721808663042</v>
+        <v>2.444766681521714</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-5.774093484621125</v>
+        <v>-6.04574586799874</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.8049844406761864</v>
+        <v>0.6963234873251403</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.466821373808737</v>
+        <v>2.440866246667409</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.086918283866105</v>
+        <v>-6.358570667243719</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.6782594410331955</v>
+        <v>0.5695984876821494</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.080261475049412</v>
+        <v>-1.123520020284958</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.465226293863738</v>
+        <v>2.43927116672241</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969596</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.091731322331442</v>
+        <v>-6.363383705709056</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.680113201576269</v>
+        <v>0.5714522482252229</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.125066654987743</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.468077288971275</v>
+        <v>2.442122161829947</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923089</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.525080430441678</v>
+        <v>-6.796732813819292</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.5027472537977715</v>
+        <v>0.394086300446725</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.125066654987743</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.464050984436871</v>
+        <v>2.438095857295544</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297751</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-6.908081819184309</v>
+        <v>-7.179734202561924</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.3494445969791347</v>
+        <v>0.2407836436280886</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.081808109752198</v>
+        <v>-1.125066654987743</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.463948883115287</v>
+        <v>2.43799375597396</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.283067145355586</v>
+        <v>-7.554719528733201</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.2020219824820542</v>
+        <v>0.09336102913100808</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.500051981159021</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.241529203383951</v>
+        <v>2.215574076242623</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.642597467859588</v>
+        <v>-7.914249851237202</v>
       </c>
       <c r="E1874" t="n">
-        <v>0.0635601567785038</v>
+        <v>-0.04510079657254273</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.456793435923476</v>
+        <v>-1.500051981159021</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.246879506682001</v>
+        <v>2.220924379540674</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-7.968997496524601</v>
+        <v>-8.240649879902215</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.05908383473032419</v>
+        <v>-0.1677447880813703</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.783193464588488</v>
+        <v>-1.826452009824034</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.058955509440171</v>
+        <v>2.033000382298844</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-7.962521349731041</v>
+        <v>-8.234173733108655</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.05345162539113124</v>
+        <v>-0.1621125787421778</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.819975863030474</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.065882948138076</v>
+        <v>2.039927820996748</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-7.95883042477463</v>
+        <v>-8.230482808152244</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.05197525540856685</v>
+        <v>-0.1606362087596134</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.776717317794929</v>
+        <v>-1.819975863030474</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.065882948138076</v>
+        <v>2.039927820996748</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.163088600104492</v>
+        <v>-8.434740983482108</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1281653284218693</v>
+        <v>-0.2368262817729163</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.904356262408918</v>
+        <v>-1.947614807644463</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.994812778488325</v>
+        <v>1.968857651346998</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.323727626592857</v>
+        <v>-8.595380009970473</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1879383845327793</v>
+        <v>-0.2965993378838263</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.019089735411313</v>
+        <v>-2.062348280646859</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.930455249171323</v>
+        <v>1.904500122029996</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.5067562600158</v>
+        <v>-8.521910178303024</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2457781364085356</v>
+        <v>-0.2518397037234257</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.202118368834256</v>
+        <v>-1.98887844897941</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.836009770610978</v>
+        <v>1.963953722523886</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.426383904551871</v>
+        <v>-8.441537822839095</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.1990739734754472</v>
+        <v>-0.2051355407903372</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.121746013370327</v>
+        <v>-1.908506093515481</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.898788404636853</v>
+        <v>2.02673235654976</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880269</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.614656706917716</v>
+        <v>-8.629810625204939</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2816022593233809</v>
+        <v>-0.2876638266382709</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.121746013370327</v>
+        <v>-1.908506093515481</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.891569239735257</v>
+        <v>2.019513191648165</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234394</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.634821348467263</v>
+        <v>-8.649975266754486</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.2963403067171759</v>
+        <v>-0.302401874032066</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.141910654919875</v>
+        <v>-1.928670735065028</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.872798264031552</v>
+        <v>2.00074221594446</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.493712438860583</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.864645795631088</v>
+        <v>-8.879799713918311</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3871542957441494</v>
+        <v>-0.3932158630590399</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.304558191990035</v>
+        <v>-2.091318272135188</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.776325531628012</v>
+        <v>1.90426948354092</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.801576563324748</v>
+        <v>-8.816730481611971</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3592328741924988</v>
+        <v>-0.3652944415073889</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.333071754672269</v>
+        <v>-2.119831834817423</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.761911122647786</v>
+        <v>1.889855074560694</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.749561049355934</v>
+        <v>-8.764714967643158</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3344363329185729</v>
+        <v>-0.3404979002334629</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.333071754672269</v>
+        <v>-2.119831834817423</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.765901458334187</v>
+        <v>1.893845410247095</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.830852978910139</v>
+        <v>-8.846006897197363</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.368428331638996</v>
+        <v>-0.3744898989538865</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.333071754672269</v>
+        <v>-2.119831834817423</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.764426231435445</v>
+        <v>1.892370183348353</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410713</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.633583573182142</v>
+        <v>-8.648737491469365</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2744671591829251</v>
+        <v>-0.2805287264978151</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.135802348944271</v>
+        <v>-1.922562429089425</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.897841285037116</v>
+        <v>2.025785236950025</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.434431465945043</v>
+        <v>-8.449585384232266</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2078574499347683</v>
+        <v>-0.2139190172496588</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.970479822994458</v>
+        <v>-1.757239903139611</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.983983666960321</v>
+        <v>2.11192761887323</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.208586313225631</v>
+        <v>-8.223740231512854</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.107940315810795</v>
+        <v>-0.114001883125685</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.928553147407294</v>
+        <v>-1.715313227552448</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.018718745348829</v>
+        <v>2.146662697261736</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.922311500902937</v>
+        <v>-7.93746541919016</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.007708753674341651</v>
+        <v>0.001647186359451158</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.928553147407294</v>
+        <v>-1.715313227552448</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.019857889904888</v>
+        <v>2.147801841817795</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.695515673829602</v>
+        <v>-7.710669592116826</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.1010608586657828</v>
+        <v>0.0949992913508928</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.86043920278575</v>
+        <v>-1.647199282930903</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.063360030839922</v>
+        <v>2.19130398275283</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.411606942900853</v>
+        <v>-7.426760861188077</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.220358055275919</v>
+        <v>0.214296487961029</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.86043920278575</v>
+        <v>-1.647199282930903</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.069093735078558</v>
+        <v>2.197037686991466</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.164619692707901</v>
+        <v>-7.179773610995125</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3094156929592349</v>
+        <v>0.3033541256443444</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.613451952592798</v>
+        <v>-1.400212032737951</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.207548822800464</v>
+        <v>2.335492774713372</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702409</v>
+        <v>3.74769908470241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.900782825503832</v>
+        <v>-6.915936743791056</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.4050669585279549</v>
+        <v>0.3990053912130644</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.613451952592798</v>
+        <v>-1.400212032737951</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.197665341487556</v>
+        <v>2.325609293400464</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906225</v>
+        <v>3.766313503906227</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.633541024635435</v>
+        <v>-6.648694942922659</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5101291183759398</v>
+        <v>0.5040675510610497</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.613451952592798</v>
+        <v>-1.400212032737951</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.195830780988183</v>
+        <v>2.323774732901091</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781949</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.357731861234951</v>
+        <v>-6.372885779522175</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6201524687626727</v>
+        <v>0.6140909014477822</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.524432644314064</v>
+        <v>-1.311192724459218</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.248942050981962</v>
+        <v>2.37688600289487</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567244</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.088664273467971</v>
+        <v>-6.103818191755195</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.728448010014958</v>
+        <v>0.7223864427000679</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.255365056547085</v>
+        <v>-1.042125136692238</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.411051109787643</v>
+        <v>2.538995061700551</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.824604335145176</v>
+        <v>-5.839758253432399</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8208116691823242</v>
+        <v>0.8147501018674341</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.9913051182242889</v>
+        <v>-0.7780651983694422</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.556226756619569</v>
+        <v>2.684170708532477</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309725</v>
+        <v>3.833249172309727</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.117524711640337</v>
+        <v>-5.132678629927561</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.100856484923959</v>
+        <v>1.094794917609069</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.9913051182242889</v>
+        <v>-0.7780651983694422</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.553439722959268</v>
+        <v>2.681383674872176</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858727</v>
+        <v>3.839370871858729</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.867883681654385</v>
+        <v>-4.883037599941609</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.201056520806181</v>
+        <v>1.194994953491291</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.7416640882383372</v>
+        <v>-0.5284241683834905</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.70356796483868</v>
+        <v>2.831511916751588</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096472</v>
+        <v>3.856158176096474</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.613341782313309</v>
+        <v>-4.628495700600533</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.302240101763368</v>
+        <v>1.296178534448478</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.4871221888972617</v>
+        <v>-0.273882269042415</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.855659925664082</v>
+        <v>2.983603877576991</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761806</v>
+        <v>3.787326853761808</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.379860560083711</v>
+        <v>-4.395014478370935</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.40355701949306</v>
+        <v>1.39749545217817</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.2536409666676631</v>
+        <v>-0.04040104681281642</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.003673087839694</v>
+        <v>3.131617039752602</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.200152029939838</v>
+        <v>-4.215305948227062</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.47254822123765</v>
+        <v>1.46648665392276</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.196469462504967</v>
+        <v>0.0167704573498797</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.035083780024352</v>
+        <v>3.163027731937261</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860426</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.206402794308332</v>
+        <v>-4.083030474596176</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.46541540223728</v>
+        <v>1.514764330122141</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.2027202268734603</v>
+        <v>0.1490459309807664</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.026700808150284</v>
+        <v>3.23776050286282</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-4.015803119635179</v>
+        <v>-3.892430799923023</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.544470332794177</v>
+        <v>1.593819260679039</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.01212055220030744</v>
+        <v>0.3396456056539192</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.143875673641812</v>
+        <v>3.354935368354348</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430982</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.766803320951599</v>
+        <v>-3.643431001239442</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.656976593491268</v>
+        <v>1.70632552137613</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.2368792464832732</v>
+        <v>0.5886454043374999</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.306181894075619</v>
+        <v>3.517241588788155</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.575424246090658</v>
+        <v>-3.452051926378502</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.605552293836426</v>
+        <v>1.654901221721287</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.4282583213442133</v>
+        <v>0.78002447919844</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.293033409392964</v>
+        <v>3.5040931041055</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.296396950435032</v>
+        <v>-3.173024630722876</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.765707553975763</v>
+        <v>1.815056481860625</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.4282583213442133</v>
+        <v>0.78002447919844</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.341577751270051</v>
+        <v>3.552637445982587</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180809</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-3.019658775764219</v>
+        <v>-2.896286456052063</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.879781835830082</v>
+        <v>1.929130763714944</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.6100749824541392</v>
+        <v>0.9618411403083658</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.454046759922001</v>
+        <v>3.665106454634537</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879203</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.892766369329149</v>
+        <v>-2.769394049616993</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.921824812150632</v>
+        <v>1.971173740035494</v>
       </c>
       <c r="F1911" t="n">
-        <v>0.7369673888892091</v>
+        <v>1.088733546743436</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.521468217529565</v>
+        <v>3.732527912242101</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568107</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.705178861419223</v>
+        <v>-2.581806541707067</v>
       </c>
       <c r="E1912" t="n">
-        <v>1.98989920321951</v>
+        <v>2.039248131104372</v>
       </c>
       <c r="F1912" t="n">
-        <v>0.7369673888892091</v>
+        <v>1.088733546743436</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.514507605434471</v>
+        <v>3.725567300147008</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.420132858879228</v>
+        <v>3.417368760020797</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.824482646428221</v>
+        <v>2.816699611486524</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.705178861419223</v>
+        <v>-2.581806541707067</v>
       </c>
       <c r="E1913" t="n">
-        <v>1.98989920321951</v>
+        <v>2.039248131104372</v>
       </c>
       <c r="F1913" t="n">
-        <v>0.7369673888892091</v>
+        <v>1.088733546743436</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.817546443414589</v>
+        <v>2.809763408472892</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -45547,7 +45547,7 @@
         <v>3.417368760020797</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.816699611486524</v>
+        <v>2.816699611486523</v>
       </c>
       <c r="D1913" t="n">
         <v>-2.581806541707067</v>
@@ -45559,7 +45559,7 @@
         <v>1.088733546743436</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.809763408472892</v>
+        <v>2.809763408472891</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998561</v>
+        <v>3.367370539998562</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.0%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,25 +801,25 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-35.0%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-66.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>105.6%</t>
+          <t>106.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-0.63</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.9%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-62.9%</t>
+          <t>-60.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.6%</t>
+          <t>87.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>653.1%</t>
+          <t>653.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-419.8%</t>
+          <t>-397.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>31.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,27 +1165,27 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.6%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.4%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.2%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-172.3%</t>
+          <t>-161.9%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>80.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.3%</t>
+          <t>94.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-24</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.6%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-13.8%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.0%</t>
+          <t>-72.0%</t>
         </is>
       </c>
     </row>
@@ -45547,19 +45547,19 @@
         <v>3.417368760020797</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.816699611486523</v>
+        <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.581806541707067</v>
+        <v>-2.357985527264165</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.039248131104372</v>
+        <v>2.143238891262675</v>
       </c>
       <c r="F1913" t="n">
         <v>1.088733546743436</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.809763408472891</v>
+        <v>3.740029654528151</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240324.xlsx
+++ b/tame_output/ON/bt/strategyON_20240324.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-15.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>26.6%</t>
         </is>
       </c>
     </row>
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-66.6%</t>
+          <t>-68.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>106.1%</t>
+          <t>106.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.63</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.4%</t>
+          <t>122.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-567.0%</t>
+          <t>-588.6%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-43.2%</t>
+          <t>-44.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-60.6%</t>
+          <t>-63.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>87.7%</t>
+          <t>88.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>653.7%</t>
+          <t>380.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-397.4%</t>
+          <t>-424.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>51.0%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>44.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>98.9%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-227.2%</t>
+          <t>-235.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>25.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-35.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>640.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-161.9%</t>
+          <t>-172.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-4.5%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.6%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>71.6%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-285.6%</t>
+          <t>-292.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-151.9%</t>
+          <t>-154.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-115.1%</t>
+          <t>-105.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.4%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>42.4%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.3%</t>
+          <t>94.6%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-171.8%</t>
+          <t>-175.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.8%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-65.9%</t>
         </is>
       </c>
     </row>
@@ -43779,16 +43779,16 @@
         <v>3.118001050765402</v>
       </c>
       <c r="D1836" t="n">
-        <v>0.4807383879894678</v>
+        <v>0.2651202623312335</v>
       </c>
       <c r="E1836" t="n">
-        <v>3.309939981647442</v>
+        <v>3.223692731384148</v>
       </c>
       <c r="F1836" t="n">
-        <v>1.823354886252747</v>
+        <v>1.759654755652646</v>
       </c>
       <c r="G1836" t="n">
-        <v>4.21201398251705</v>
+        <v>4.173793904156989</v>
       </c>
     </row>
     <row r="1837">
@@ -43802,16 +43802,16 @@
         <v>3.118490189491276</v>
       </c>
       <c r="D1837" t="n">
-        <v>0.4865877691047122</v>
+        <v>0.2709696434464778</v>
       </c>
       <c r="E1837" t="n">
-        <v>3.312768872819414</v>
+        <v>3.22652162255612</v>
       </c>
       <c r="F1837" t="n">
-        <v>1.823354886252747</v>
+        <v>1.759654755652646</v>
       </c>
       <c r="G1837" t="n">
-        <v>4.212503121242924</v>
+        <v>4.174283042882864</v>
       </c>
     </row>
     <row r="1838">
@@ -43825,16 +43825,16 @@
         <v>3.122570172112943</v>
       </c>
       <c r="D1838" t="n">
-        <v>0.4383655022576287</v>
+        <v>0.2227473765993943</v>
       </c>
       <c r="E1838" t="n">
-        <v>3.297559948702247</v>
+        <v>3.211312698438953</v>
       </c>
       <c r="F1838" t="n">
-        <v>1.775132619405663</v>
+        <v>1.711432488805563</v>
       </c>
       <c r="G1838" t="n">
-        <v>4.18764974375634</v>
+        <v>4.149429665396281</v>
       </c>
     </row>
     <row r="1839">
@@ -43848,16 +43848,16 @@
         <v>3.157511256610484</v>
       </c>
       <c r="D1839" t="n">
-        <v>0.2012340104078336</v>
+        <v>-0.01438411525040079</v>
       </c>
       <c r="E1839" t="n">
-        <v>3.237648436459871</v>
+        <v>3.151401186196577</v>
       </c>
       <c r="F1839" t="n">
-        <v>1.775132619405663</v>
+        <v>1.711432488805563</v>
       </c>
       <c r="G1839" t="n">
-        <v>4.222590828253883</v>
+        <v>4.184370749893822</v>
       </c>
     </row>
     <row r="1840">
@@ -43871,16 +43871,16 @@
         <v>3.156088696795822</v>
       </c>
       <c r="D1840" t="n">
-        <v>0.2062716011354201</v>
+        <v>-0.009346524522814259</v>
       </c>
       <c r="E1840" t="n">
-        <v>3.238240912936243</v>
+        <v>3.151993662672949</v>
       </c>
       <c r="F1840" t="n">
-        <v>1.83077707567198</v>
+        <v>1.76707694507188</v>
       </c>
       <c r="G1840" t="n">
-        <v>4.254554942199011</v>
+        <v>4.21633486383895</v>
       </c>
     </row>
     <row r="1841">
@@ -43894,16 +43894,16 @@
         <v>3.13483507841956</v>
       </c>
       <c r="D1841" t="n">
-        <v>0.1498019699591233</v>
+        <v>-0.06581615569911103</v>
       </c>
       <c r="E1841" t="n">
-        <v>3.194399442089462</v>
+        <v>3.108152191826168</v>
       </c>
       <c r="F1841" t="n">
-        <v>1.774307444495683</v>
+        <v>1.710607313895583</v>
       </c>
       <c r="G1841" t="n">
-        <v>4.19941954511697</v>
+        <v>4.161199466756909</v>
       </c>
     </row>
     <row r="1842">
@@ -43917,16 +43917,16 @@
         <v>3.13585268755003</v>
       </c>
       <c r="D1842" t="n">
-        <v>0.08403457990971125</v>
+        <v>-0.1315835457485231</v>
       </c>
       <c r="E1842" t="n">
-        <v>3.169110095200167</v>
+        <v>3.082862844936873</v>
       </c>
       <c r="F1842" t="n">
-        <v>1.774307444495683</v>
+        <v>1.710607313895583</v>
       </c>
       <c r="G1842" t="n">
-        <v>4.20043715424744</v>
+        <v>4.16221707588738</v>
       </c>
     </row>
     <row r="1843">
@@ -43940,16 +43940,16 @@
         <v>3.126480719537785</v>
       </c>
       <c r="D1843" t="n">
-        <v>0.07049909613300165</v>
+        <v>-0.1451190295252327</v>
       </c>
       <c r="E1843" t="n">
-        <v>3.154323933677239</v>
+        <v>3.068076683413945</v>
       </c>
       <c r="F1843" t="n">
-        <v>1.774307444495683</v>
+        <v>1.710607313895583</v>
       </c>
       <c r="G1843" t="n">
-        <v>4.191065186235195</v>
+        <v>4.152845107875136</v>
       </c>
     </row>
     <row r="1844">
@@ -43963,16 +43963,16 @@
         <v>3.116563445493024</v>
       </c>
       <c r="D1844" t="n">
-        <v>-0.01127280429475003</v>
+        <v>-0.2268909299529844</v>
       </c>
       <c r="E1844" t="n">
-        <v>3.111697899461376</v>
+        <v>3.025450649198083</v>
       </c>
       <c r="F1844" t="n">
-        <v>1.80134301790182</v>
+        <v>1.737642887301719</v>
       </c>
       <c r="G1844" t="n">
-        <v>4.197369256234116</v>
+        <v>4.159149177874055</v>
       </c>
     </row>
     <row r="1845">
@@ -43986,16 +43986,16 @@
         <v>3.121328762326726</v>
       </c>
       <c r="D1845" t="n">
-        <v>-0.0784819121666277</v>
+        <v>-0.294100037824862</v>
       </c>
       <c r="E1845" t="n">
-        <v>3.089579573146327</v>
+        <v>3.003332322883034</v>
       </c>
       <c r="F1845" t="n">
-        <v>1.80134301790182</v>
+        <v>1.737642887301719</v>
       </c>
       <c r="G1845" t="n">
-        <v>4.202134573067818</v>
+        <v>4.163914494707758</v>
       </c>
     </row>
     <row r="1846">
@@ -44009,16 +44009,16 @@
         <v>3.119153558445966</v>
       </c>
       <c r="D1846" t="n">
-        <v>-0.0744904593714375</v>
+        <v>-0.2901085850296719</v>
       </c>
       <c r="E1846" t="n">
-        <v>3.089000950383644</v>
+        <v>3.00275370012035</v>
       </c>
       <c r="F1846" t="n">
-        <v>1.80533447069701</v>
+        <v>1.74163434009691</v>
       </c>
       <c r="G1846" t="n">
-        <v>4.202354240864173</v>
+        <v>4.164134162504112</v>
       </c>
     </row>
     <row r="1847">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.4726388903246981</v>
+        <v>-0.6882570159829324</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.927668469507403</v>
+        <v>2.841421219244109</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.407186039743749</v>
+        <v>1.343485909143649</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.961392073797279</v>
+        <v>3.923171995437219</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.6942608238828156</v>
+        <v>-0.90987894954105</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.838885912683078</v>
+        <v>2.752638662419784</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.36965990605638</v>
+        <v>1.30595977545628</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.938742610183779</v>
+        <v>3.900522531823719</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9022648822358929</v>
+        <v>-1.117883007894127</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.760576433895772</v>
+        <v>2.674329183632478</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.36965990605638</v>
+        <v>1.30595977545628</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.943634754737705</v>
+        <v>3.905414676377645</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.172664844944778</v>
+        <v>-1.388282970603013</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.647497905150206</v>
+        <v>2.561250654886912</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.099259943347495</v>
+        <v>1.035559812747395</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.776476233450362</v>
+        <v>3.738256155090302</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.5118232225333</v>
+        <v>-1.727441348191535</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.504918853421246</v>
+        <v>2.418671603157952</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7601015657589729</v>
+        <v>0.6964014351588725</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.566065506203698</v>
+        <v>3.527845427843638</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.839840444260779</v>
+        <v>-2.055458569919014</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.394050254469023</v>
+        <v>2.307803004205729</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.4320843440314938</v>
+        <v>0.3683842134313934</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.389593462905979</v>
+        <v>3.351373384545918</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-1.836503697751808</v>
+        <v>-2.052121823410042</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.40348370348118</v>
+        <v>2.317236453217886</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.4347763764505251</v>
+        <v>0.3710762458504248</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.399307432765966</v>
+        <v>3.361087354405905</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.203214749418353</v>
+        <v>-2.418832875076588</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.257905674858294</v>
+        <v>2.171658424595</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.06806532478397953</v>
+        <v>0.004365194183879151</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.180387193809771</v>
+        <v>3.14216711544971</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-2.588395140348426</v>
+        <v>-2.804013266006661</v>
       </c>
       <c r="E1855" t="n">
-        <v>2.102376057299129</v>
+        <v>2.016128807035835</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.06806532478397953</v>
+        <v>0.004365194183879151</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.178929732622634</v>
+        <v>3.140709654262574</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-2.932077913575089</v>
+        <v>-3.147696039233323</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.966672071463079</v>
+        <v>1.880424821199786</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.03984072724323867</v>
+        <v>-0.1035408578433391</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.115955224860919</v>
+        <v>3.077735146500859</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.289728263813437</v>
+        <v>-3.505346389471671</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.819717990023998</v>
+        <v>1.733470739760704</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.3974910774815868</v>
+        <v>-0.4611912080816872</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.897471073374168</v>
+        <v>2.859250995014108</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.296389204035584</v>
+        <v>-3.512007329693819</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.818826540635398</v>
+        <v>1.732579290372104</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.3974910774815868</v>
+        <v>-0.4611912080816872</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.899244000074428</v>
+        <v>2.861023921714367</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-3.728194997185372</v>
+        <v>-3.943813122843607</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.632437110842887</v>
+        <v>1.546189860579594</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.5339085739228537</v>
+        <v>-0.5976087045229541</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.803726389677072</v>
+        <v>2.765506311317012</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.054627526053116</v>
+        <v>-4.270245651711351</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.490148874297881</v>
+        <v>1.403901624034587</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.6163768244300019</v>
+        <v>-0.6800769550301022</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.742530214374874</v>
+        <v>2.704310136014814</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.056191677163419</v>
+        <v>-4.271809802821654</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.488103805509724</v>
+        <v>1.401856555246431</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.6163768244300019</v>
+        <v>-0.6800769550301022</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.741110806030839</v>
+        <v>2.702890727670779</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.419817922063732</v>
+        <v>-4.635436047721967</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.349140867783841</v>
+        <v>1.262893617520547</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.7145984612971277</v>
+        <v>-0.7782985918972281</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.688665384144805</v>
+        <v>2.650445305784745</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-4.417390857535014</v>
+        <v>-4.633008983193249</v>
       </c>
       <c r="E1863" t="n">
-        <v>1.34936620860116</v>
+        <v>1.263118958337866</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.7149312431042794</v>
+        <v>-0.7786313737043797</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.687720230066345</v>
+        <v>2.649500151706285</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-4.825979634715693</v>
+        <v>-5.041597760373927</v>
       </c>
       <c r="E1864" t="n">
-        <v>1.184692241743647</v>
+        <v>1.098444991480354</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.441328507772697</v>
+        <v>2.403108429412637</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.238962118856787</v>
+        <v>-5.454580244515021</v>
       </c>
       <c r="E1865" t="n">
-        <v>1.01468468055867</v>
+        <v>0.9284374302953768</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.436513940244158</v>
+        <v>2.398293861884098</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-5.655353993143784</v>
+        <v>-5.870972118802018</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.8461219814527485</v>
+        <v>0.7598747311894551</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.434507990853035</v>
+        <v>2.396287912492975</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.032031003673628</v>
+        <v>-6.247649129331863</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.7057098679094898</v>
+        <v>0.6194626176461964</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.444766681521714</v>
+        <v>2.406546603161654</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.04574586799874</v>
+        <v>-6.261363993656974</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.6963234873251403</v>
+        <v>0.6100762370618469</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.440866246667409</v>
+        <v>2.402646168307349</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-6.358570667243719</v>
+        <v>-6.574188792901953</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.5695984876821494</v>
+        <v>0.483351237418856</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.123520020284958</v>
+        <v>-1.187220150885058</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.43927116672241</v>
+        <v>2.40105108836235</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-6.363383705709056</v>
+        <v>-6.57900183136729</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.5714522482252229</v>
+        <v>0.4852049979619295</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.125066654987743</v>
+        <v>-1.188766785587844</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.442122161829947</v>
+        <v>2.403902083469887</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-6.796732813819292</v>
+        <v>-7.012350939477527</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.394086300446725</v>
+        <v>0.3078390501834321</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.125066654987743</v>
+        <v>-1.188766785587844</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.438095857295544</v>
+        <v>2.399875778935484</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.179734202561924</v>
+        <v>-7.395352328220158</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.2407836436280886</v>
+        <v>0.1545363933647952</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.125066654987743</v>
+        <v>-1.188766785587844</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.43799375597396</v>
+        <v>2.3997736776139</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.554719528733201</v>
+        <v>-7.770337654391435</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.09336102913100808</v>
+        <v>0.007113778867714693</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.500051981159021</v>
+        <v>-1.563752111759121</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.215574076242623</v>
+        <v>2.177353997882563</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-7.914249851237202</v>
+        <v>-8.129867976895436</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.04510079657254273</v>
+        <v>-0.1313480468358357</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.500051981159021</v>
+        <v>-1.563752111759121</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.220924379540674</v>
+        <v>2.182704301180614</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.240649879902215</v>
+        <v>-8.45626800556045</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1677447880813703</v>
+        <v>-0.2539920383446637</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.826452009824034</v>
+        <v>-1.890152140424134</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.033000382298844</v>
+        <v>1.994780303938783</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.234173733108655</v>
+        <v>-8.44979185876689</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1621125787421778</v>
+        <v>-0.2483598290054707</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.819975863030474</v>
+        <v>-1.883675993630574</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.039927820996748</v>
+        <v>2.001707742636688</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.230482808152244</v>
+        <v>-8.446100933810479</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1606362087596134</v>
+        <v>-0.2468834590229068</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.819975863030474</v>
+        <v>-1.883675993630574</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.039927820996748</v>
+        <v>2.001707742636688</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.434740983482108</v>
+        <v>-8.650359109140343</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2368262817729163</v>
+        <v>-0.3230735320362097</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.947614807644463</v>
+        <v>-2.011314938244563</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.968857651346998</v>
+        <v>1.930637572986937</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.595380009970473</v>
+        <v>-8.810998135628708</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2965993378838263</v>
+        <v>-0.3828465881471197</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.062348280646859</v>
+        <v>-2.126048411246959</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.904500122029996</v>
+        <v>1.866280043669936</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.521910178303024</v>
+        <v>-8.737528303961259</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2518397037234257</v>
+        <v>-0.3380869539867191</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.98887844897941</v>
+        <v>-2.052578579579511</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.963953722523886</v>
+        <v>1.925733644163826</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.441537822839095</v>
+        <v>-8.65715594849733</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2051355407903372</v>
+        <v>-0.2913827910536306</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.908506093515481</v>
+        <v>-1.972206224115581</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.02673235654976</v>
+        <v>1.988512278189701</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.629810625204939</v>
+        <v>-8.845428750863174</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.2876638266382709</v>
+        <v>-0.3739110769015643</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.908506093515481</v>
+        <v>-1.972206224115581</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.019513191648165</v>
+        <v>1.981293113288104</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-8.649975266754486</v>
+        <v>-8.865593392412721</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.302401874032066</v>
+        <v>-0.3886491242953594</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.928670735065028</v>
+        <v>-1.992370865665128</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.00074221594446</v>
+        <v>1.9625221375844</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-8.879799713918311</v>
+        <v>-9.095417839576546</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.3932158630590399</v>
+        <v>-0.4794631133223328</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.091318272135188</v>
+        <v>-2.155018402735289</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.90426948354092</v>
+        <v>1.86604940518086</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-8.816730481611971</v>
+        <v>-9.032348607270206</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.3652944415073889</v>
+        <v>-0.4515416917706823</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.119831834817423</v>
+        <v>-2.183531965417523</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.889855074560694</v>
+        <v>1.851634996200634</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-8.764714967643158</v>
+        <v>-8.980333093301393</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.3404979002334629</v>
+        <v>-0.4267451504967563</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.119831834817423</v>
+        <v>-2.183531965417523</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.893845410247095</v>
+        <v>1.855625331887035</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-8.846006897197363</v>
+        <v>-9.061625022855598</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.3744898989538865</v>
+        <v>-0.4607371492171799</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.119831834817423</v>
+        <v>-2.183531965417523</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.892370183348353</v>
+        <v>1.854150104988293</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-8.648737491469365</v>
+        <v>-8.8643556171276</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.2805287264978151</v>
+        <v>-0.3667759767611085</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.922562429089425</v>
+        <v>-1.986262559689525</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.025785236950025</v>
+        <v>1.987565158589964</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-8.449585384232266</v>
+        <v>-8.665203509890501</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.2139190172496588</v>
+        <v>-0.3001662675129517</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.757239903139611</v>
+        <v>-1.820940033739712</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.11192761887323</v>
+        <v>2.073707540513169</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.223740231512854</v>
+        <v>-8.439358357171091</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.114001883125685</v>
+        <v>-0.2002491333889793</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.715313227552448</v>
+        <v>-1.779013358152548</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.146662697261736</v>
+        <v>2.108442618901676</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-7.93746541919016</v>
+        <v>-8.153083544848396</v>
       </c>
       <c r="E1891" t="n">
-        <v>0.001647186359451158</v>
+        <v>-0.08460006390384223</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.715313227552448</v>
+        <v>-1.779013358152548</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.147801841817795</v>
+        <v>2.109581763457735</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-7.710669592116826</v>
+        <v>-7.926287717775063</v>
       </c>
       <c r="E1892" t="n">
-        <v>0.0949992913508928</v>
+        <v>0.008752041087598528</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.647199282930903</v>
+        <v>-1.710899413531004</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.19130398275283</v>
+        <v>2.153083904392769</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-7.426760861188077</v>
+        <v>-7.642378986846314</v>
       </c>
       <c r="E1893" t="n">
-        <v>0.214296487961029</v>
+        <v>0.1280492376977347</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.647199282930903</v>
+        <v>-1.710899413531004</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.197037686991466</v>
+        <v>2.158817608631406</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-7.179773610995125</v>
+        <v>-7.395391736653361</v>
       </c>
       <c r="E1894" t="n">
-        <v>0.3033541256443444</v>
+        <v>0.2171068753810506</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.400212032737951</v>
+        <v>-1.463912163338052</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.335492774713372</v>
+        <v>2.297272696353312</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-6.915936743791056</v>
+        <v>-7.131554869449293</v>
       </c>
       <c r="E1895" t="n">
-        <v>0.3990053912130644</v>
+        <v>0.3127581409497706</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.400212032737951</v>
+        <v>-1.463912163338052</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.325609293400464</v>
+        <v>2.287389215040404</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-6.648694942922659</v>
+        <v>-6.864313068580896</v>
       </c>
       <c r="E1896" t="n">
-        <v>0.5040675510610497</v>
+        <v>0.4178203007977555</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.400212032737951</v>
+        <v>-1.463912163338052</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.323774732901091</v>
+        <v>2.285554654541031</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-6.372885779522175</v>
+        <v>-6.588503905180412</v>
       </c>
       <c r="E1897" t="n">
-        <v>0.6140909014477822</v>
+        <v>0.5278436511844884</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.311192724459218</v>
+        <v>-1.374892855059318</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37688600289487</v>
+        <v>2.33866592453481</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-6.103818191755195</v>
+        <v>-6.319436317413432</v>
       </c>
       <c r="E1898" t="n">
-        <v>0.7223864427000679</v>
+        <v>0.6361391924367736</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.042125136692238</v>
+        <v>-1.105825267292339</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.538995061700551</v>
+        <v>2.500774983340491</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-5.839758253432399</v>
+        <v>-6.055376379090636</v>
       </c>
       <c r="E1899" t="n">
-        <v>0.8147501018674341</v>
+        <v>0.7285028516041399</v>
       </c>
       <c r="F1899" t="n">
-        <v>-0.7780651983694422</v>
+        <v>-0.8417653289695426</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.684170708532477</v>
+        <v>2.645950630172416</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-5.132678629927561</v>
+        <v>-5.348296755585798</v>
       </c>
       <c r="E1900" t="n">
-        <v>1.094794917609069</v>
+        <v>1.008547667345775</v>
       </c>
       <c r="F1900" t="n">
-        <v>-0.7780651983694422</v>
+        <v>-0.8417653289695426</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.681383674872176</v>
+        <v>2.643163596512116</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-4.883037599941609</v>
+        <v>-5.098655725599846</v>
       </c>
       <c r="E1901" t="n">
-        <v>1.194994953491291</v>
+        <v>1.108747703227997</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.5284241683834905</v>
+        <v>-0.5921242989835909</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.831511916751588</v>
+        <v>2.793291838391528</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-4.628495700600533</v>
+        <v>-4.84411382625877</v>
       </c>
       <c r="E1902" t="n">
-        <v>1.296178534448478</v>
+        <v>1.209931284185184</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.273882269042415</v>
+        <v>-0.3375823996425154</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.983603877576991</v>
+        <v>2.94538379921693</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-4.395014478370935</v>
+        <v>-4.610632604029171</v>
       </c>
       <c r="E1903" t="n">
-        <v>1.39749545217817</v>
+        <v>1.311248201914876</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.04040104681281642</v>
+        <v>-0.1041011774129168</v>
       </c>
       <c r="G1903" t="n">
-        <v>3.131617039752602</v>
+        <v>3.093396961392542</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-4.215305948227062</v>
+        <v>-4.430924073885299</v>
       </c>
       <c r="E1904" t="n">
-        <v>1.46648665392276</v>
+        <v>1.380239403659466</v>
       </c>
       <c r="F1904" t="n">
-        <v>0.0167704573498797</v>
+        <v>-0.04692967325022068</v>
       </c>
       <c r="G1904" t="n">
-        <v>3.163027731937261</v>
+        <v>3.1248076535772</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-4.083030474596176</v>
+        <v>-4.298648600254412</v>
       </c>
       <c r="E1905" t="n">
-        <v>1.514764330122141</v>
+        <v>1.428517079858847</v>
       </c>
       <c r="F1905" t="n">
-        <v>0.1490459309807664</v>
+        <v>0.08534580038066597</v>
       </c>
       <c r="G1905" t="n">
-        <v>3.23776050286282</v>
+        <v>3.199540424502759</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-3.892430799923023</v>
+        <v>-4.10804892558126</v>
       </c>
       <c r="E1906" t="n">
-        <v>1.593819260679039</v>
+        <v>1.507572010415745</v>
       </c>
       <c r="F1906" t="n">
-        <v>0.3396456056539192</v>
+        <v>0.2759454750538188</v>
       </c>
       <c r="G1906" t="n">
-        <v>3.354935368354348</v>
+        <v>3.316715289994288</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-3.643431001239442</v>
+        <v>-3.859049126897679</v>
       </c>
       <c r="E1907" t="n">
-        <v>1.70632552137613</v>
+        <v>1.620078271112836</v>
       </c>
       <c r="F1907" t="n">
-        <v>0.5886454043374999</v>
+        <v>0.5249452737373995</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.517241588788155</v>
+        <v>3.479021510428095</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-3.452051926378502</v>
+        <v>-3.667670052036739</v>
       </c>
       <c r="E1908" t="n">
-        <v>1.654901221721287</v>
+        <v>1.568653971457993</v>
       </c>
       <c r="F1908" t="n">
-        <v>0.78002447919844</v>
+        <v>0.7163243485983396</v>
       </c>
       <c r="G1908" t="n">
-        <v>3.5040931041055</v>
+        <v>3.46587302574544</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-3.173024630722876</v>
+        <v>-3.388642756381112</v>
       </c>
       <c r="E1909" t="n">
-        <v>1.815056481860625</v>
+        <v>1.72880923159733</v>
       </c>
       <c r="F1909" t="n">
-        <v>0.78002447919844</v>
+        <v>0.7163243485983396</v>
       </c>
       <c r="G1909" t="n">
-        <v>3.552637445982587</v>
+        <v>3.514417367622527</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-2.896286456052063</v>
+        <v>-3.1119045817103</v>
       </c>
       <c r="E1910" t="n">
-        <v>1.929130763714944</v>
+        <v>1.84288351345165</v>
       </c>
       <c r="F1910" t="n">
-        <v>0.9618411403083658</v>
+        <v>0.8981410097082654</v>
       </c>
       <c r="G1910" t="n">
-        <v>3.665106454634537</v>
+        <v>3.626886376274477</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-2.769394049616993</v>
+        <v>-2.98501217527523</v>
       </c>
       <c r="E1911" t="n">
-        <v>1.971173740035494</v>
+        <v>1.8849264897722</v>
       </c>
       <c r="F1911" t="n">
-        <v>1.088733546743436</v>
+        <v>1.025033416143335</v>
       </c>
       <c r="G1911" t="n">
-        <v>3.732527912242101</v>
+        <v>3.694307833882041</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-2.581806541707067</v>
+        <v>-2.797424667365303</v>
       </c>
       <c r="E1912" t="n">
-        <v>2.039248131104372</v>
+        <v>1.953000880841078</v>
       </c>
       <c r="F1912" t="n">
-        <v>1.088733546743436</v>
+        <v>1.025033416143335</v>
       </c>
       <c r="G1912" t="n">
-        <v>3.725567300147008</v>
+        <v>3.687347221786947</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.417368760020797</v>
+        <v>3.546982796139814</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-2.357985527264165</v>
+        <v>-2.632442658074735</v>
       </c>
       <c r="E1913" t="n">
-        <v>2.143238891262675</v>
+        <v>2.033456038938448</v>
       </c>
       <c r="F1913" t="n">
-        <v>1.088733546743436</v>
+        <v>1.190015425433904</v>
       </c>
       <c r="G1913" t="n">
-        <v>3.740029654528151</v>
+        <v>3.800798781742432</v>
       </c>
     </row>
   </sheetData>
